--- a/Customer_Segmentation_Analysis_Amaan.xlsx
+++ b/Customer_Segmentation_Analysis_Amaan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Amaan laptop data\Data Science\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC64C24-A1F6-4BBF-A798-CA85BB7C702C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AACB37-C1F9-4B12-9630-7399FB8D9B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F2FD5835-93FB-423B-8347-62D6DACEA082}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{F2FD5835-93FB-423B-8347-62D6DACEA082}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId5"/>
+    <pivotCache cacheId="7" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -892,12 +892,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1251,7 +1251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1298,12 +1298,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1322,31 +1316,13 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1354,27 +1330,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1383,17 +1352,31 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1402,83 +1385,35 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="64">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <sz val="16"/>
@@ -1601,6 +1536,36 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <sz val="16"/>
       </font>
     </dxf>
@@ -1627,6 +1592,36 @@
     <dxf>
       <font>
         <sz val="16"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
       </font>
     </dxf>
     <dxf>
@@ -2293,7 +2288,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[practice lc2.xlsx]Pivot Tablw!PivotTable1</c:name>
+    <c:name>[Customer_Segmentation_Analysis_Amaan.xlsx]Pivot Tablw!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -2388,39 +2383,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill>
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1"/>
-                </a:gs>
-                <a:gs pos="46000">
-                  <a:schemeClr val="accent1"/>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="20000"/>
-                    <a:lumOff val="80000"/>
-                    <a:alpha val="0"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:path path="circle">
-                <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-              </a:path>
-            </a:gradFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:shade val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2777,7 +2740,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[practice lc2.xlsx]Pivot Tablw!PivotTable3</c:name>
+    <c:name>[Customer_Segmentation_Analysis_Amaan.xlsx]Pivot Tablw!PivotTable3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -2858,8 +2821,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2920,8 +2882,8 @@
           <c:idx val="0"/>
           <c:layout>
             <c:manualLayout>
-              <c:x val="0.10841160275326413"/>
-              <c:y val="0.1988306577484707"/>
+              <c:x val="7.8900629566057964E-2"/>
+              <c:y val="0.21257635228852573"/>
             </c:manualLayout>
           </c:layout>
           <c:spPr>
@@ -2981,8 +2943,8 @@
           <c:idx val="0"/>
           <c:layout>
             <c:manualLayout>
-              <c:x val="-6.9398150775082212E-2"/>
-              <c:y val="0.1690655822549971"/>
+              <c:x val="-4.7264896425229734E-2"/>
+              <c:y val="0.13813764003444004"/>
             </c:manualLayout>
           </c:layout>
           <c:spPr>
@@ -3022,8 +2984,8 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
               <c15:layout>
                 <c:manualLayout>
-                  <c:w val="0.12980011926216198"/>
-                  <c:h val="7.0089258569983506E-2"/>
+                  <c:w val="9.5370776299564392E-2"/>
+                  <c:h val="7.6961916260473648E-2"/>
                 </c:manualLayout>
               </c15:layout>
             </c:ext>
@@ -3061,35 +3023,6 @@
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -3213,8 +3146,8 @@
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-6.9398150775082212E-2"/>
-                  <c:y val="0.1690655822549971"/>
+                  <c:x val="-4.7264896425229734E-2"/>
+                  <c:y val="0.13813764003444004"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr>
@@ -3254,8 +3187,8 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout>
                     <c:manualLayout>
-                      <c:w val="0.12980011926216198"/>
-                      <c:h val="7.0089258569983506E-2"/>
+                      <c:w val="9.5370776299564392E-2"/>
+                      <c:h val="7.6961916260473648E-2"/>
                     </c:manualLayout>
                   </c15:layout>
                 </c:ext>
@@ -3268,8 +3201,8 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.10841160275326413"/>
-                  <c:y val="0.1988306577484707"/>
+                  <c:x val="7.8900629566057964E-2"/>
+                  <c:y val="0.21257635228852573"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="bestFit"/>
@@ -3516,7 +3449,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[practice lc2.xlsx]Pivot Tablw!PivotTable4</c:name>
+    <c:name>[Customer_Segmentation_Analysis_Amaan.xlsx]Pivot Tablw!PivotTable4</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -5635,9 +5568,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>857250</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>962025</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5665,15 +5598,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>95251</xdr:colOff>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>95251</xdr:rowOff>
+      <xdr:rowOff>95252</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>1304926</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5700,15 +5633,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>471488</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>547688</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:colOff>933450</xdr:colOff>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>37899</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6654,7 +6587,157 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E5F9360-1143-4CAB-88CB-3F4AC6BD1422}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{97362C73-6CA4-4A44-AFEB-7C02C2BD2AB3}" name="PivotTable4" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+  <location ref="E2:F7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="16">
+        <item x="2"/>
+        <item x="13"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="12"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="10"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item h="1" x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Customer_Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="11">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="12" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="12" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleDark23" showRowHeaders="1" showColHeaders="1" showRowStripes="1" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E5F9360-1143-4CAB-88CB-3F4AC6BD1422}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="B2:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -6714,16 +6797,16 @@
     <dataField name="Sum of Total_Spent" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="18">
-    <format dxfId="0">
+    <format dxfId="29">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="27">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="3">
@@ -6734,22 +6817,22 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="23">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="21">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="3">
@@ -6760,22 +6843,22 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="17">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="15">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="3">
@@ -6786,10 +6869,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -6825,8 +6908,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{381393A2-6758-44EF-9E94-82F3081FE9E0}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{381393A2-6758-44EF-9E94-82F3081FE9E0}" name="PivotTable3" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="B8:C13" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
     <pivotField showAll="0"/>
@@ -6907,48 +6990,48 @@
     <dataField name="Sum of Total_Spent" fld="8" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="18">
+    <format dxfId="41">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="40">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="39">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="12" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="35">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="34">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="33">
       <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="12" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -7006,156 +7089,6 @@
           </reference>
           <reference field="12" count="1" selected="0">
             <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleDark23" showRowHeaders="1" showColHeaders="1" showRowStripes="1" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{97362C73-6CA4-4A44-AFEB-7C02C2BD2AB3}" name="PivotTable4" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
-  <location ref="E2:F7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="16">
-        <item x="2"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="12"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="10"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item h="1" x="4"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="12"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Customer_Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="30">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="31">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="12" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="34">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="37">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="38">
-      <pivotArea field="12" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="39">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="12" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="40">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="41">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -9468,7 +9401,7 @@
       <c r="N36" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O36" s="16">
+      <c r="O36" s="14">
         <f>COUNTIF(Table1[Membership],"Silver")</f>
         <v>16</v>
       </c>
@@ -10109,7 +10042,7 @@
       <c r="N48" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="O48" s="16">
+      <c r="O48" s="14">
         <f>COUNTIF(Table1[Membership],"Gold")</f>
         <v>9</v>
       </c>
@@ -10319,86 +10252,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
     </row>
     <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:16" ht="27.75" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="43" t="s">
         <v>273</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="54" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="47" t="s">
         <v>274</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="56" t="s">
+      <c r="F4" s="48"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="34" t="s">
         <v>275</v>
       </c>
-      <c r="I4" s="57"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="58" t="s">
+      <c r="I4" s="35"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="38" t="s">
         <v>276</v>
       </c>
-      <c r="L4" s="59"/>
+      <c r="L4" s="39"/>
     </row>
     <row r="5" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="43">
+      <c r="A5" s="45">
         <v>50</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="E5" s="45">
+      <c r="B5" s="46"/>
+      <c r="E5" s="49">
         <f>SUM(Table1[Total_Spent])</f>
         <v>4065832</v>
       </c>
-      <c r="F5" s="46"/>
-      <c r="H5" s="47" t="str">
+      <c r="F5" s="50"/>
+      <c r="H5" s="36" t="str">
         <f>INDEX('Pivot Tablw'!B3:B5,MATCH(MAX('Pivot Tablw'!C3:C5),'Pivot Tablw'!C3:C5,0))</f>
         <v>Noida</v>
       </c>
-      <c r="I5" s="48"/>
-      <c r="K5" s="49" t="str">
+      <c r="I5" s="37"/>
+      <c r="K5" s="40" t="str">
         <f>INDEX(Table1[Membership],MATCH(MAX(Table1[Total_Spent]),Table1[Total_Spent],0))</f>
         <v>Platinum</v>
       </c>
-      <c r="L5" s="50"/>
+      <c r="L5" s="41"/>
     </row>
     <row r="6" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -10431,128 +10364,128 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="24" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="40">
+      <c r="C3" s="29">
         <v>515602</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="36">
+      <c r="F3" s="24">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="40">
+      <c r="C4" s="29">
         <v>501067</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="24">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="29">
         <v>680967</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="24">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="29">
         <v>1697636</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="24">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="24">
         <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="24" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="31">
         <v>8.5037453588834952E-2</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="31">
         <v>0.22474194703568667</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="31">
         <v>0.48637622016846738</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="31">
         <v>0.20384437920701101</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="21" x14ac:dyDescent="0.35">
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="31">
         <v>1</v>
       </c>
     </row>
@@ -10572,106 +10505,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="51" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="54" t="s">
         <v>247</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="16" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="19" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="21" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="21" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="21" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="21" t="s">
         <v>271</v>
       </c>
     </row>
